--- a/site/StructureDefinition-hcen-encounter.xlsx
+++ b/site/StructureDefinition-hcen-encounter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3861" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3861" uniqueCount="575">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T01:23:13-03:00</t>
+    <t>2026-10-28T18:02:56-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1065,10 +1065,10 @@
     <t>Encounter.participant</t>
   </si>
   <si>
-    <t>Profesional involucrado en el evento clínico</t>
-  </si>
-  <si>
-    <t>Identifica al profesional (p.ej. PractitionerRole) involucrado en el evento clínico.</t>
+    <t>Profesional involucrado en el evento clínico — al menos uno, con la hora de firma en period.start</t>
+  </si>
+  <si>
+    <t>Identifica al profesional (p.ej. PractitionerRole) involucrado en el evento clínico. Al menos un participant debe estar presente para registrar la hora de firma en period.start.</t>
   </si>
   <si>
     <t>ClinicalDocument/author/assignedAuthor</t>
@@ -1147,10 +1147,10 @@
 </t>
   </si>
   <si>
-    <t>Starting time with inclusive boundary</t>
-  </si>
-  <si>
-    <t>The start of the period. The boundary is inclusive.</t>
+    <t>Hora de firma del profesional — única ubicación disponible en esta guía para este dato</t>
+  </si>
+  <si>
+    <t>Hora de firma del profesional (mapea a ClinicalDocument/author/time en CDA, donde es obligatoria). No existe otra ubicación en esta guía para este dato.</t>
   </si>
   <si>
     <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
@@ -1274,6 +1274,12 @@
   </si>
   <si>
     <t>Encounter.period.start</t>
+  </si>
+  <si>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
   </si>
   <si>
     <t>ClinicalDocument/componentOf/encompassingEncounter/effectiveTime/low/@value</t>
@@ -8346,7 +8352,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>80</v>
@@ -8929,7 +8935,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>88</v>
@@ -9276,7 +9282,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>88</v>
@@ -10109,10 +10115,10 @@
         <v>365</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>366</v>
+        <v>408</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>367</v>
+        <v>409</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>368</v>
@@ -10180,7 +10186,7 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>20</v>
@@ -10197,10 +10203,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10299,7 +10305,7 @@
         <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>20</v>
@@ -10316,10 +10322,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10342,16 +10348,16 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10401,7 +10407,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10422,25 +10428,25 @@
         <v>401</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10462,13 +10468,13 @@
         <v>213</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10497,10 +10503,10 @@
         <v>112</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -10518,7 +10524,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10536,28 +10542,28 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10576,16 +10582,16 @@
         <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10635,7 +10641,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10653,24 +10659,24 @@
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10696,10 +10702,10 @@
         <v>164</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10750,7 +10756,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10771,7 +10777,7 @@
         <v>20</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>20</v>
@@ -10782,10 +10788,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10897,10 +10903,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11014,10 +11020,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11133,14 +11139,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11159,16 +11165,16 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11218,7 +11224,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>88</v>
@@ -11236,24 +11242,24 @@
         <v>20</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11279,10 +11285,10 @@
         <v>213</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11312,10 +11318,10 @@
         <v>112</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>20</v>
@@ -11333,7 +11339,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11365,10 +11371,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11391,13 +11397,13 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11448,7 +11454,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11469,7 +11475,7 @@
         <v>20</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>20</v>
@@ -11480,10 +11486,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11506,16 +11512,16 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11565,7 +11571,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11586,7 +11592,7 @@
         <v>20</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>20</v>
@@ -11597,10 +11603,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11626,13 +11632,13 @@
         <v>164</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11682,7 +11688,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11703,7 +11709,7 @@
         <v>20</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>20</v>
@@ -11714,10 +11720,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11829,10 +11835,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11946,10 +11952,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12065,10 +12071,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12094,10 +12100,10 @@
         <v>145</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12148,7 +12154,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12175,15 +12181,15 @@
         <v>20</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12206,13 +12212,13 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12263,7 +12269,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12284,7 +12290,7 @@
         <v>20</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>20</v>
@@ -12295,10 +12301,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12324,10 +12330,10 @@
         <v>213</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12357,10 +12363,10 @@
         <v>112</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>20</v>
@@ -12378,7 +12384,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12399,21 +12405,21 @@
         <v>20</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12439,10 +12445,10 @@
         <v>213</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12472,10 +12478,10 @@
         <v>287</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>20</v>
@@ -12493,7 +12499,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12520,15 +12526,15 @@
         <v>20</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12554,16 +12560,16 @@
         <v>213</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -12591,10 +12597,10 @@
         <v>287</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>20</v>
@@ -12612,7 +12618,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12633,21 +12639,21 @@
         <v>20</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12673,10 +12679,10 @@
         <v>213</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12706,10 +12712,10 @@
         <v>112</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>20</v>
@@ -12727,7 +12733,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12748,21 +12754,21 @@
         <v>20</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12788,10 +12794,10 @@
         <v>213</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12821,10 +12827,10 @@
         <v>112</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>20</v>
@@ -12842,7 +12848,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12863,21 +12869,21 @@
         <v>20</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12900,13 +12906,13 @@
         <v>20</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12957,7 +12963,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12978,21 +12984,21 @@
         <v>20</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13018,10 +13024,10 @@
         <v>213</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13051,10 +13057,10 @@
         <v>287</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>20</v>
@@ -13072,7 +13078,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13093,21 +13099,21 @@
         <v>20</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13133,13 +13139,13 @@
         <v>164</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13189,7 +13195,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13210,7 +13216,7 @@
         <v>20</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>20</v>
@@ -13221,10 +13227,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13336,10 +13342,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13453,10 +13459,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13572,10 +13578,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13598,13 +13604,13 @@
         <v>20</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13655,7 +13661,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>88</v>
@@ -13673,24 +13679,24 @@
         <v>20</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>387</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13716,13 +13722,13 @@
         <v>108</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13751,10 +13757,10 @@
         <v>156</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>20</v>
@@ -13772,7 +13778,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13793,7 +13799,7 @@
         <v>20</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>20</v>
@@ -13804,10 +13810,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13833,13 +13839,13 @@
         <v>213</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13868,10 +13874,10 @@
         <v>287</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>20</v>
@@ -13889,7 +13895,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13921,10 +13927,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13950,10 +13956,10 @@
         <v>187</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14004,7 +14010,7 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14036,10 +14042,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14062,13 +14068,13 @@
         <v>20</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14119,7 +14125,7 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14134,27 +14140,27 @@
         <v>100</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>386</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14177,16 +14183,16 @@
         <v>20</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14236,7 +14242,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14254,10 +14260,10 @@
         <v>20</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>20</v>
